--- a/output/pdf_financials_xlsx/SURE.xlsx
+++ b/output/pdf_financials_xlsx/SURE.xlsx
@@ -1641,10 +1641,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.405056</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.405056</v>
       </c>
     </row>
     <row r="93">
@@ -2556,7 +2556,11 @@
           <t>Share-based payment reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" s="5" t="n">
         <v>0.405056</v>
       </c>

--- a/output/pdf_financials_xlsx/SURE.xlsx
+++ b/output/pdf_financials_xlsx/SURE.xlsx
@@ -553,10 +553,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.211186</v>
+        <v>0.279888</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.182168</v>
+        <v>0.241968</v>
       </c>
     </row>
     <row r="11">
@@ -879,10 +879,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.134802</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.023493</v>
       </c>
     </row>
     <row r="35">
@@ -905,10 +905,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.134802</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.023493</v>
       </c>
     </row>
     <row r="37">
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.144958</v>
+        <v>0.010156</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.049702</v>
+        <v>0.026209</v>
       </c>
     </row>
     <row r="49">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E34" s="5" t="n">
